--- a/run-artifacts/QuickFlow-prompts-sessions.xlsx
+++ b/run-artifacts/QuickFlow-prompts-sessions.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prompts'!$A$1:$H$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sessions'!$A$1:$T$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Milestones'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prompts'!$A$1:$H$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sessions'!$A$1:$T$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Milestones'!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1556,40 +1556,880 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:23:44+03:00</t>
+          <t>2026-10-15T00:19:28.702Z</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:30:55.676Z</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress and where we now the percentage for first task</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:31:32.560Z</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>&lt;task-notification&gt;
+&lt;task-id&gt;byle2hrqn&lt;/task-id&gt;
+&lt;tool-use-id&gt;toolu_01UyNs3t7q8Egi5kNTh4uFqy&lt;/tool-use-id&gt;
+&lt;output-file&gt;/tmp/claude-1000/-home-ahmoh-Documents-proj-demo-QuickFlow/31c1aee4-c1ac-4453-ab53-e63ee45afb9f/tasks/byle2hrqn.output&lt;/output-file&gt;
+&lt;status&gt;completed&lt;/status&gt;
+&lt;summary&gt;Background command "Run the M01 pipeline (BE and FE loops, then verify)" completed (exit code 0)&lt;/summary&gt;
+&lt;/task-notification&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:34:36.765Z</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>start all of milestones one by one (once one finishes procced to the next without approval)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:45:46.970Z</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>&lt;task-notification&gt;
+&lt;task-id&gt;bjsvfikv1&lt;/task-id&gt;
+&lt;tool-use-id&gt;toolu_013AADuSi6GxqHvjN63D3uGM&lt;/tool-use-id&gt;
+&lt;output-file&gt;/tmp/claude-1000/-home-ahmoh-Documents-proj-demo-QuickFlow/31c1aee4-c1ac-4453-ab53-e63ee45afb9f/tasks/bjsvfikv1.output&lt;/output-file&gt;
+&lt;status&gt;completed&lt;/status&gt;
+&lt;summary&gt;Background command "Run pipeline for M02 through M07 unattended" completed (exit code 0)&lt;/summary&gt;
+&lt;/task-notification&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T03:32:07.605Z</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>&lt;task-notification&gt;
+&lt;task-id&gt;bj7zetv95&lt;/task-id&gt;
+&lt;tool-use-id&gt;toolu_01Tvfv5uMxefupPnFPYDnon8&lt;/tool-use-id&gt;
+&lt;status&gt;stopped&lt;/status&gt;
+&lt;summary&gt;Background shell command didn't finish before the previous session ended&lt;/summary&gt;
+&lt;note&gt;No completion record was found for it in the previous session. It may have been stopped (via the UI, Monitor timeout, or agent teardown — these leave no transcript marker), or it may have been running when the previous Claude Code process exited. Check the output file for partial results before assuming it completed.&lt;/note&gt;
+&lt;/task-notification&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T03:33:31.262Z</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T03:40:25.327Z</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:36:52.699Z</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:38:40.334Z</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T07:56:24.631Z</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:08:12.831Z</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:14:10.853Z</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>&lt;task-notification&gt;
+&lt;task-id&gt;bmoh3kd0y&lt;/task-id&gt;
+&lt;tool-use-id&gt;toolu_014P1929wukg97HqjVGubiwv&lt;/tool-use-id&gt;
+&lt;output-file&gt;/tmp/claude-1000/-home-ahmoh-Documents-proj-demo-QuickFlow/31c1aee4-c1ac-4453-ab53-e63ee45afb9f/tasks/bmoh3kd0y.output&lt;/output-file&gt;
+&lt;status&gt;completed&lt;/status&gt;
+&lt;summary&gt;Background command "Restart pipeline from M06 under a sleep inhibitor" completed (exit code 0)&lt;/summary&gt;
+&lt;/task-notification&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:49:35.701Z</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>show me the progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:50:27.662Z</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>run the app</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:54:41.234Z</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>let's plan to some enhancements in the FE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:56:33.095Z</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:58:24.793Z</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:05:09.163Z</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:11:50.184Z</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>what is the need of the 3 new scripts ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:13:28.841Z</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>no need for them all</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:14:54.125Z</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:16:06.268Z</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:18:45.412Z</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>interactive</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>planning-002</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>31c1aee4-c1ac-4453-ab53-e63ee45afb9f</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:23</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>5f3887c1-b7fc-4fbc-90bb-8807c863932f</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M01, trial 0, iteration 1, model claude-haiku-5-5.
@@ -1604,43 +2444,43 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:26:30+03:00</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>02f2e09b-1d61-4285-9fcb-6aece5161837</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M01, trial 0, iteration 2, model claude-haiku-5-5.
@@ -1655,43 +2495,43 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:26:49+03:00</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>e0bace24-e51f-487f-99e9-9bfa6140c755</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M01, trial 0, iteration 1, model claude-haiku-5-5.
@@ -1706,43 +2546,43 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:31:30+03:00</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:31</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>M01</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>0bfdae0a-cf0a-4ef5-ba0b-816ac173d118</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
 Verify milestone M01, round 1 (trial 0 so far), on the real stack that is already running:
@@ -1759,43 +2599,43 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:37:21+03:00</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:37</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>97932feb-8330-4b57-b3f5-0c99298097bb</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M02, trial 0, iteration 1, model claude-haiku-5-5.
@@ -1810,43 +2650,43 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:39:57+03:00</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:39</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>0ea9eebd-ce80-4e53-a355-05a332116a6b</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M02, trial 0, iteration 1, model claude-haiku-5-5.
@@ -1861,43 +2701,43 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:40:02+03:00</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:40</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>a4e5321c-7cba-42e9-a9ce-aa01ffda7bbe</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M02, trial 0, iteration 2, model claude-haiku-5-5.
@@ -1912,43 +2752,43 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:45:45+03:00</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:45</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>M02</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>c384f6c1-6d92-4c78-b4d2-5f662572a438</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
 Verify milestone M02, round 1 (trial 0 so far), on the real stack that is already running:
@@ -1965,43 +2805,43 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:48:37+03:00</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:48</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>77b3ff87-cf56-4514-a9a4-bbfe8f393d01</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M03, trial 0, iteration 1, model claude-haiku-5-5.
@@ -2016,43 +2856,43 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:51:01+03:00</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:51</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>2e9bfce7-ea7b-495a-a3d1-8465374443f3</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M03, trial 0, iteration 1, model claude-haiku-5-5.
@@ -2067,43 +2907,43 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:51:19+03:00</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:51</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>a12b89cd-62a1-46ce-a2ae-782834209f08</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M03, trial 0, iteration 2, model claude-haiku-5-5.
@@ -2118,43 +2958,43 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:52:08+03:00</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:52</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>b990e0d4-d980-4957-abfa-0121707cad1e</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M03, trial 0, iteration 3, model claude-haiku-5-5.
@@ -2169,43 +3009,43 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:53:49+03:00</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:53</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>0dd4f066-1b73-480d-b7d5-5cfdb3686173</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M03, trial 0, iteration 4, model claude-haiku-5-5.
@@ -2220,43 +3060,43 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:55:14+03:00</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:55</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>b8489630-2728-46fd-8588-66f6df498647</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M03, trial 1, iteration 5, model claude-haiku-5-5.
@@ -2271,43 +3111,43 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T03:59:34+03:00</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 6:59</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>M03</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>e85391e2-f87f-418c-a5dd-2822e228dfb7</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
 Verify milestone M03, round 1 (trial 1 so far), on the real stack that is already running:
@@ -2324,43 +3164,43 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T04:02:11+03:00</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 7:02</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>M04</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>d4d79dd7-fecf-4209-9e6c-7d56923b0588</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M04, trial 0, iteration 1, model claude-haiku-5-5.
@@ -2375,43 +3215,43 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T04:02:17+03:00</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 7:02</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>M04</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>9b9b8c9b-a239-4736-af06-7ca94f64acbd</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M04, trial 0, iteration 1, model claude-haiku-5-5.
@@ -2426,43 +3266,43 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T04:04:12+03:00</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 7:04</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>M04</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>98548a41-6526-4bac-9b4d-6e14caddc0ae</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M04, trial 0, iteration 2, model claude-haiku-5-5.
@@ -2477,43 +3317,43 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T04:05:28+03:00</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 7:05</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>M04</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>bf5840f4-7d0c-4ebc-b6db-d99ef5e9cd83</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M04, trial 0, iteration 2, model claude-haiku-5-5.
@@ -2528,43 +3368,43 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T04:10:53+03:00</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 7:10</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>M04</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>568fca4f-9bcb-46b3-a658-d4ec485abd87</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
 Verify milestone M04, round 1 (trial 0 so far), on the real stack that is already running:
@@ -2581,43 +3421,43 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T06:36:32+03:00</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 9:36</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>M05</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>91ef3e79-22c9-4565-b730-59a7d5bd49a6</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M05, trial 0, iteration 2, model claude-haiku-5-5.
@@ -2632,43 +3472,43 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T06:37:57+03:00</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 9:37</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>M05</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>c1b36576-5445-47a4-bc62-c3327a0e0ec5</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M05, trial 0, iteration 2, model claude-haiku-5-5.
@@ -2683,43 +3523,43 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T06:40:14+03:00</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 9:40</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>M05</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>527c37c6-d36e-4fe7-a4d0-9072a64e873c</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M05, trial 0, iteration 3, model claude-haiku-5-5.
@@ -2734,43 +3574,43 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T06:41:33+03:00</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 9:41</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>M05</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>933527ae-f854-4b0d-9643-568701c8f61e</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M05, trial 0, iteration 3, model claude-haiku-5-5.
@@ -2785,43 +3625,43 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T06:45:28+03:00</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 9:45</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>M05</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>fe239e73-8d98-4cac-87d2-7b6963ab7aa4</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M05, trial 0, iteration 4, model claude-haiku-5-5.
@@ -2836,43 +3676,43 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T06:54:39+03:00</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 9:54</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>M05</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>fcda09fc-cf2c-4f73-adc5-0737c232c05e</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
 Verify milestone M05, round 1 (trial 0 so far), on the real stack that is already running:
@@ -2889,43 +3729,43 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T10:41:07+03:00</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 13:41</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>M06</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>e462b62e-80f1-406f-a6fa-100562e48c97</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M06, trial 0, iteration 2, model claude-haiku-5-5.
@@ -2940,43 +3780,43 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T10:44:56+03:00</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 13:44</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>M06</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>ab6a2c50-0cd9-4686-a4a9-c258d13c6533</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M06, trial 0, iteration 2, model claude-haiku-5-5.
@@ -2991,43 +3831,43 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T10:51:45+03:00</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 13:51</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>M06</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>c55e7178-3681-43f0-ad14-4ad11035d93a</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
 Verify milestone M06, round 1 (trial 0 so far), on the real stack that is already running:
@@ -3044,43 +3884,43 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T10:58:53+03:00</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 13:58</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>M07</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>5ee29270-3d60-40f4-a392-f337df3bd7a3</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M07, trial 0, iteration 1, model claude-haiku-5-5.
@@ -3095,43 +3935,43 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T11:00:19+03:00</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 14:00</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>M07</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>b7334588-7362-4734-9556-dfb07d8ce6d0</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the backend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M07, trial 0, iteration 1, model claude-haiku-5-5.
@@ -3146,43 +3986,43 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T11:04:15+03:00</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 14:04</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>frontend-dev</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>M07</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>claude-haiku-5-5</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>a96bb28a-f940-4b9e-aacc-8326841938a1</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
 This is ONE iteration: milestone M07, trial 0, iteration 2, model claude-haiku-5-5.
@@ -3197,43 +4037,43 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15T11:14:09+03:00</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>10/15/26 14:14</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>headless</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>M07</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>979d24b3-e173-40e6-bb83-97400db8ceb4</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
 Verify milestone M07, round 1 (trial 0 so far), on the real stack that is already running:
@@ -3250,8 +4090,1189 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:22:44+03:00</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>4515dcfa-0049-49c3-8a38-3bf9eaf94441</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M08, trial 0, iteration 1, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:28:54+03:00</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>58ae77bd-fd12-4afd-9bf5-bd4122ae493d</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M08, trial 0, iteration 2, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:36:19+03:00</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>8fc70025-e646-4d16-a9c5-adeef4d1e115</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
+Verify milestone M08, round 1 (trial 0 so far), on the real stack that is already running:
+backend http://localhost:8090 (fresh stable database), frontend http://localhost:4300 proxying to it.
+Follow loops/_shared/PROTOCOL.md and loops/verify/Loop-instructions.md. Read, in order: CLAUDE.md,
+.specify/memory/constitution.md, loops/verify/Loop-instructions.md, loops/verify/task.md, loops/verify/state/handoff.md (if it exists).
+Run every check (review of git diff HEAD + untracked files, Swagger diff, ./mvnw verify, curl regression,
+this milestone's Playwright scenarios end to end with the Playwright MCP, smoke scenarios of earlier milestones).
+Fix small issues yourself (&lt;= 3 files, &lt;= ~30 lines, no design or contract change), log each fix and re-run the affected checks.
+Write loops/verify/outputs/M08-round-1.md, evidence under loops/verify/outputs/evidence/M08/round-1/, append to loops/verify/progress.md,
+rewrite loops/verify/state/handoff.md, and write loops/verify/state/verdict.json as the very last step. Then stop.
+Never ask questions and never commit.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:39:33+03:00</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>e9c1e405-32c9-4d39-b6f5-46276349836b</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M09, trial 0, iteration 1, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:45:25+03:00</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>9a429d3c-6a70-4bb4-8f0d-23d7fa78abbb</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M09, trial 0, iteration 2, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:59:15+03:00</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>c88491dd-58e9-4596-85d7-6cd90e7962c8</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
+Verify milestone M09, round 1 (trial 0 so far), on the real stack that is already running:
+backend http://localhost:8090 (fresh stable database), frontend http://localhost:4300 proxying to it.
+Follow loops/_shared/PROTOCOL.md and loops/verify/Loop-instructions.md. Read, in order: CLAUDE.md,
+.specify/memory/constitution.md, loops/verify/Loop-instructions.md, loops/verify/task.md, loops/verify/state/handoff.md (if it exists).
+Run every check (review of git diff HEAD + untracked files, Swagger diff, ./mvnw verify, curl regression,
+this milestone's Playwright scenarios end to end with the Playwright MCP, smoke scenarios of earlier milestones).
+Fix small issues yourself (&lt;= 3 files, &lt;= ~30 lines, no design or contract change), log each fix and re-run the affected checks.
+Write loops/verify/outputs/M09-round-1.md, evidence under loops/verify/outputs/evidence/M09/round-1/, append to loops/verify/progress.md,
+rewrite loops/verify/state/handoff.md, and write loops/verify/state/verdict.json as the very last step. Then stop.
+Never ask questions and never commit.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:04:24+03:00</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>891ab029-2bd5-47b2-b931-79dc6496d3af</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M10, trial 0, iteration 1, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:10:51+03:00</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>a7847923-c292-4b9b-b1ac-27adb88c7cb4</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M10, trial 0, iteration 2, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:16:53+03:00</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>d6892d77-7cfe-4c9a-be43-d8b83549fc21</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M10, trial 0, iteration 3, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:20:44+03:00</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>af2e0024-9568-45b3-b690-b3fba08a6417</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M10, trial 0, iteration 4, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:36:10+03:00</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>07d02b0c-7a6c-41ed-b6c8-b35eadd13082</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
+Verify milestone M10, round 1 (trial 0 so far), on the real stack that is already running:
+backend http://localhost:8090 (fresh stable database), frontend http://localhost:4300 proxying to it.
+Follow loops/_shared/PROTOCOL.md and loops/verify/Loop-instructions.md. Read, in order: CLAUDE.md,
+.specify/memory/constitution.md, loops/verify/Loop-instructions.md, loops/verify/task.md, loops/verify/state/handoff.md (if it exists).
+Run every check (review of git diff HEAD + untracked files, Swagger diff, ./mvnw verify, curl regression,
+this milestone's Playwright scenarios end to end with the Playwright MCP, smoke scenarios of earlier milestones).
+Fix small issues yourself (&lt;= 3 files, &lt;= ~30 lines, no design or contract change), log each fix and re-run the affected checks.
+Write loops/verify/outputs/M10-round-1.md, evidence under loops/verify/outputs/evidence/M10/round-1/, append to loops/verify/progress.md,
+rewrite loops/verify/state/handoff.md, and write loops/verify/state/verdict.json as the very last step. Then stop.
+Never ask questions and never commit.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:45:53+03:00</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>b84512ad-8116-45a9-a102-42e6be0d5b9c</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 0, iteration 1, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:58:16+03:00</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>fff0e995-e172-4c9d-978e-a356c898947a</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 0, iteration 2, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:01:28+03:00</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>d79fb430-a0f8-4e27-8871-5bafe3720e9c</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 0, iteration 3, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:03:30+03:00</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>800a34be-2af2-4918-b83b-14c034944e30</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 0, iteration 4, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:05:47+03:00</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>c662ec5b-4892-4a79-99ad-9090a899abf7</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 0, iteration 5, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:07:44+03:00</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>db77f81a-86c9-4758-a7aa-5e3227ffb80a</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 1, iteration 6, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:11:31+03:00</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>92cc1784-0662-42b3-85f8-bfae5dc23f4b</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 1, iteration 7, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:26:44+03:00</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>c2608ec7-0d45-4185-a65d-5ee831b906a1</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 1, iteration 8, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:28:11+03:00</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>c1526f46-20b8-4120-9e55-b0e0bcb114ef</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 1, iteration 9, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:30:27+03:00</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>029d1e45-06b3-4acd-b26d-039395aa4883</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 3, iteration 10, model claude-sonnet-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:28:12+03:00</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>8c2a1cf2-be53-4bf5-9035-5477852c2377</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the frontend-dev loop of the QuickFlow project (the project root is the current directory).
+This is ONE iteration: milestone M11, trial 0, iteration 11, model claude-haiku-5-5.
+Follow loops/_shared/PROTOCOL.md exactly. Read, in order: CLAUDE.md, .specify/memory/constitution.md,
+loops/frontend-dev/Loop-instructions.md, loops/frontend-dev/task.md, loops/frontend-dev/state/handoff.md (if it exists),
+then your milestone file named in task.md.
+Do FIX tasks first, then at most 5 open tasks. Run the self-check from your Loop-instructions.
+Tick only finished, self-checked tasks. Append to the action log in loops/frontend-dev/progress.md, rewrite
+loops/frontend-dev/state/handoff.md, and write loops/frontend-dev/state/result.json as the very last step. Then stop.
+Never ask questions, never commit, never edit the contract, stop every server you started.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:40:02+03:00</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>headless</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>aab71505-9c77-496f-9044-7f4a512a6154</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You are the verify loop of the QuickFlow project (the project root is the current directory).
+Verify milestone M11, round 1 (trial 0 so far), on the real stack that is already running:
+backend http://localhost:8090 (fresh stable database), frontend http://localhost:4300 proxying to it.
+Follow loops/_shared/PROTOCOL.md and loops/verify/Loop-instructions.md. Read, in order: CLAUDE.md,
+.specify/memory/constitution.md, loops/verify/Loop-instructions.md, loops/verify/task.md, loops/verify/state/handoff.md (if it exists).
+Run every check (review of git diff HEAD + untracked files, Swagger diff, ./mvnw verify, curl regression,
+this milestone's Playwright scenarios end to end with the Playwright MCP, smoke scenarios of earlier milestones).
+Fix small issues yourself (&lt;= 3 files, &lt;= ~30 lines, no design or contract change), log each fix and re-run the affected checks.
+Write loops/verify/outputs/M11-round-1.md, evidence under loops/verify/outputs/evidence/M11/round-1/, append to loops/verify/progress.md,
+rewrite loops/verify/state/handoff.md, and write loops/verify/state/verdict.json as the very last step. Then stop.
+Never ask questions and never commit.
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H62"/>
+  <autoFilter ref="A1:H109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3262,7 +5283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:T57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3392,7 +5413,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:23:44+03:00</t>
+          <t>10/15/26 6:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3490,7 +5511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:26:30+03:00</t>
+          <t>10/15/26 6:26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -3588,7 +5609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:26:49+03:00</t>
+          <t>10/15/26 6:26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3686,7 +5707,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:31:30+03:00</t>
+          <t>10/15/26 6:31</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3784,7 +5805,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:37:21+03:00</t>
+          <t>10/15/26 6:37</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3882,7 +5903,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:39:57+03:00</t>
+          <t>10/15/26 6:39</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3980,7 +6001,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:40:02+03:00</t>
+          <t>10/15/26 6:40</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4078,7 +6099,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:45:45+03:00</t>
+          <t>10/15/26 6:45</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -4176,7 +6197,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:48:37+03:00</t>
+          <t>10/15/26 6:48</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4274,7 +6295,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:51:01+03:00</t>
+          <t>10/15/26 6:51</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -4372,7 +6393,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:51:19+03:00</t>
+          <t>10/15/26 6:51</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4470,7 +6491,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:52:08+03:00</t>
+          <t>10/15/26 6:52</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -4568,7 +6589,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:53:49+03:00</t>
+          <t>10/15/26 6:53</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -4666,7 +6687,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:55:14+03:00</t>
+          <t>10/15/26 6:55</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -4764,7 +6785,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T03:59:34+03:00</t>
+          <t>10/15/26 6:59</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -4862,7 +6883,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:02:11+03:00</t>
+          <t>10/15/26 7:02</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -4960,7 +6981,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:02:17+03:00</t>
+          <t>10/15/26 7:02</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -5058,7 +7079,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:04:12+03:00</t>
+          <t>10/15/26 7:04</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -5156,7 +7177,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:05:28+03:00</t>
+          <t>10/15/26 7:05</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -5254,7 +7275,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T04:10:53+03:00</t>
+          <t>10/15/26 7:10</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -5352,7 +7373,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:36:32+03:00</t>
+          <t>10/15/26 9:36</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -5450,7 +7471,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:37:57+03:00</t>
+          <t>10/15/26 9:37</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -5548,7 +7569,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:14+03:00</t>
+          <t>10/15/26 9:40</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -5646,7 +7667,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:41:33+03:00</t>
+          <t>10/15/26 9:41</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -5744,7 +7765,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:45:28+03:00</t>
+          <t>10/15/26 9:45</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -5842,7 +7863,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:54:39+03:00</t>
+          <t>10/15/26 9:54</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -5940,7 +7961,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T10:41:07+03:00</t>
+          <t>10/15/26 13:41</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -6038,7 +8059,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T10:44:56+03:00</t>
+          <t>10/15/26 13:44</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -6136,7 +8157,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T10:51:45+03:00</t>
+          <t>10/15/26 13:51</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -6234,7 +8255,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T10:58:53+03:00</t>
+          <t>10/15/26 13:58</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -6332,7 +8353,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T11:00:19+03:00</t>
+          <t>10/15/26 14:00</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -6430,7 +8451,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T11:04:15+03:00</t>
+          <t>10/15/26 14:04</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -6528,7 +8549,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T11:14:09+03:00</t>
+          <t>10/15/26 14:14</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -6623,8 +8644,2262 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:22:44+03:00</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>4515dcfa-0049-49c3-8a38-3bf9eaf94441</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M08-t0-i1.md</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>36043</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2044882</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>88630</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.062518</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>220184</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M08-t0-i1-20261015-121858.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:28:54+03:00</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>58ae77bd-fd12-4afd-9bf5-bd4122ae493d</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M08-t0-i2.md</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>71845</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4993172</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>171820</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.396774</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>364364</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M08-t0-i2-20261015-122244.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:36:19+03:00</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>8fc70025-e646-4d16-a9c5-adeef4d1e115</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/verify/M08-round-1.md</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>30373</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>4713225</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>157241</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>2.808425</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>414731</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/verify/M08-t0-i1-20261015-122919.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:39:33+03:00</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>e9c1e405-32c9-4d39-b6f5-46276349836b</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M09-t0-i1.md</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>34609</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>1561067</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>93667</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.077689</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>185405</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M09-t0-i1-20261015-123621.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:45:25+03:00</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>9a429d3c-6a70-4bb4-8f0d-23d7fa78abbb</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M09-t0-i2.md</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>45808</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>8680989</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>174766</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.561251</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>341066</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M09-t0-i2-20261015-123934.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:59:15+03:00</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>c88491dd-58e9-4596-85d7-6cd90e7962c8</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/verify/M09-round-1.md</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>33136</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>8096989</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>195284</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>3.844942</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>797731</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/verify/M09-t0-i1-20261015-124552.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:04:24+03:00</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>891ab029-2bd5-47b2-b931-79dc6496d3af</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M10-t0-i1.md</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>46253</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2277052</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>111654</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.137789</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>298958</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M10-t0-i1-20261015-125918.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:10:51+03:00</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>a7847923-c292-4b9b-b1ac-27adb88c7cb4</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M10-t0-i2.md</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>61939</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>4852297</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>161460</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.373293</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>375706</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M10-t0-i2-20261015-130425.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:16:53+03:00</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>d6892d77-7cfe-4c9a-be43-d8b83549fc21</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M10-t0-i3.md</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>41478</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5296718</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>184676</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.409475</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>352851</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M10-t0-i3-20261015-131051.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:20:44+03:00</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>af2e0024-9568-45b3-b690-b3fba08a6417</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M10-t0-i4.md</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>22947</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2136185</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>104423</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.120412</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>221970</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M10-t0-i4-20261015-131653.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:36:10+03:00</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>07d02b0c-7a6c-41ed-b6c8-b35eadd13082</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/verify/M10-round-1.md</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>45029</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>10940696</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>237836</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>4.992063</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>815583</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/verify/M10-t0-i1-20261015-132227.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:45:53+03:00</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>b84512ad-8116-45a9-a102-42e6be0d5b9c</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t0-i1.md</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>53933</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>8275510</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>192152</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.569356</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>570472</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t0-i1-20261015-133613.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:58:16+03:00</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>fff0e995-e172-4c9d-978e-a356c898947a</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t0-i2.md</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>56153</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>20162780</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>303678</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>1.231277</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>733656</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t0-i2-20261015-134554.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:01:28+03:00</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>d79fb430-a0f8-4e27-8871-5bafe3720e9c</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t0-i3.md</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>10758</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>739880</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>45586</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.021899</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>182485</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t0-i3-20261015-135817.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:03:30+03:00</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>800a34be-2af2-4918-b83b-14c034944e30</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t0-i4.md</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>558309</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>51123</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.020369</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>107678</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t0-i4-20261015-140129.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:05:47+03:00</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>c662ec5b-4892-4a79-99ad-9090a899abf7</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t0-i5.md</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>11072</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>776474</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>53988</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.024102</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>127961</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t0-i5-20261015-140331.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:07:44+03:00</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>db77f81a-86c9-4758-a7aa-5e3227ffb80a</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t1-i6.md</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>10281</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>732450</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>60547</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.024577</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>108577</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t1-i6-20261015-140548.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:11:31+03:00</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>92cc1784-0662-42b3-85f8-bfae5dc23f4b</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t1-i7.md</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>20534</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>1637577</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>98401</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.107244</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>216641</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t1-i7-20261015-140745.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:26:44+03:00</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>c2608ec7-0d45-4185-a65d-5ee831b906a1</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t1-i8.md</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>104528</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>27271847</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>439095</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>1.927858</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>904365</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t1-i8-20261015-141131.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:28:11+03:00</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>c1526f46-20b8-4120-9e55-b0e0bcb114ef</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t1-i9.md</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>8910</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>298565</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>33927</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.014228</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>78483</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t1-i9-20261015-142645.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T14:30:27+03:00</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5-5</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>029d1e45-06b3-4acd-b26d-039395aa4883</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t3-i10.md</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>6367</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>548258</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>37461</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.268400</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>125433</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t3-i10-20261015-142812.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:28:12+03:00</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>claude-haiku-5-5</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>8c2a1cf2-be53-4bf5-9035-5477852c2377</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/frontend-dev/M11-t0-i11.md</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>13736</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>1691404</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>119145</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.109026</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>92770</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/frontend-dev/M11-t0-i11-20261015-172637.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:40:02+03:00</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>specs/002-visual-polish</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>verify</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>aab71505-9c77-496f-9044-7f4a512a6154</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/prompts/verify/M11-round-1.md</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>39627</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>9018243</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>199174</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>4.190157</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>676654</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>run-artifacts/logs/verify/M11-t0-i1-20261015-172841.json</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T34"/>
+  <autoFilter ref="A1:T57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6635,7 +10910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7091,8 +11366,220 @@
       </c>
       <c r="M8" s="2" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Design foundation</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:18:58+03:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:36:21+03:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>3.2677</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Shell and navigation</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:36:21+03:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:59:17+03:00</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>4.4839</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pages</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:59:18+03:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:36:12+03:00</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>6.033</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Polish and regression</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T13:36:13+03:00</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T17:40:04+03:00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>8.5085</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>